--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_tarapaca.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.01949322121546</v>
+      </c>
+      <c r="C2">
         <v>24.4973057235575</v>
-      </c>
-      <c r="C2">
-        <v>29.01949322121546</v>
       </c>
       <c r="D2">
         <v>4.08208156147704</v>
       </c>
       <c r="E2">
-        <v>15.95741045406392</v>
+        <v>18.90313856248077</v>
       </c>
       <c r="F2">
         <v>65.13945098345529</v>
       </c>
       <c r="G2">
-        <v>18.90313856248077</v>
+        <v>15.95741045406392</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>40.23526920990301</v>
+      </c>
+      <c r="C3">
         <v>13.56569145065036</v>
-      </c>
-      <c r="C3">
-        <v>40.23526920990301</v>
       </c>
       <c r="D3">
         <v>7.371537261022239</v>
       </c>
       <c r="E3">
-        <v>8.820290453575607</v>
+        <v>26.16060981485306</v>
       </c>
       <c r="F3">
         <v>65.01909973157134</v>
       </c>
       <c r="G3">
-        <v>26.16060981485306</v>
+        <v>8.820290453575607</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>39.49090165610304</v>
+      </c>
+      <c r="C4">
         <v>20.74217951339195</v>
-      </c>
-      <c r="C4">
-        <v>39.49090165610304</v>
       </c>
       <c r="D4">
         <v>4.821094135041893</v>
       </c>
       <c r="E4">
-        <v>12.94500446599464</v>
+        <v>24.64591042490749</v>
       </c>
       <c r="F4">
         <v>62.40908510909787</v>
       </c>
       <c r="G4">
-        <v>24.64591042490749</v>
+        <v>12.94500446599464</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>44.92753623188405</v>
+      </c>
+      <c r="C5">
         <v>40.25764895330113</v>
-      </c>
-      <c r="C5">
-        <v>44.92753623188405</v>
       </c>
       <c r="D5">
         <v>2.484</v>
       </c>
       <c r="E5">
-        <v>21.73913043478261</v>
+        <v>24.26086956521739</v>
       </c>
       <c r="F5">
         <v>54</v>
       </c>
       <c r="G5">
-        <v>24.26086956521739</v>
+        <v>21.73913043478261</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>40.3921568627451</v>
+      </c>
+      <c r="C6">
         <v>35.88235294117647</v>
-      </c>
-      <c r="C6">
-        <v>40.3921568627451</v>
       </c>
       <c r="D6">
         <v>2.786885245901639</v>
       </c>
       <c r="E6">
-        <v>20.3559510567297</v>
+        <v>22.91434927697442</v>
       </c>
       <c r="F6">
         <v>56.72969966629589</v>
       </c>
       <c r="G6">
-        <v>22.91434927697442</v>
+        <v>20.3559510567297</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>47.24919093851133</v>
+      </c>
+      <c r="C7">
         <v>31.84466019417476</v>
-      </c>
-      <c r="C7">
-        <v>47.24919093851133</v>
       </c>
       <c r="D7">
         <v>3.140243902439024</v>
       </c>
       <c r="E7">
-        <v>17.7809902421395</v>
+        <v>26.38236357065414</v>
       </c>
       <c r="F7">
         <v>55.83664618720636</v>
       </c>
       <c r="G7">
-        <v>26.38236357065414</v>
+        <v>17.7809902421395</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>39.99429060805024</v>
+      </c>
+      <c r="C8">
         <v>32.62917499286326</v>
-      </c>
-      <c r="C8">
-        <v>39.99429060805024</v>
       </c>
       <c r="D8">
         <v>3.064741907261592</v>
       </c>
       <c r="E8">
-        <v>18.90193484372416</v>
+        <v>23.16851331238631</v>
       </c>
       <c r="F8">
         <v>57.92955184388953</v>
       </c>
       <c r="G8">
-        <v>23.16851331238631</v>
+        <v>18.90193484372416</v>
       </c>
     </row>
   </sheetData>
